--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v6/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v6/EVAL_SUMMARY.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,16 +541,134 @@
         <v>58</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4235294117647059</v>
+        <v>0.423529</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3829787234042553</v>
+        <v>0.382979</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4022346368715084</v>
+        <v>0.402235</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5753968253968254</v>
+        <v>0.575397</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>llama3.2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>contrary_v6</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>check-in</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Contrary(P)Body(N)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>252</v>
+      </c>
+      <c r="H3" t="n">
+        <v>34</v>
+      </c>
+      <c r="I3" t="n">
+        <v>111</v>
+      </c>
+      <c r="J3" t="n">
+        <v>47</v>
+      </c>
+      <c r="K3" t="n">
+        <v>60</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.419753</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.361702</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.388571</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.575397</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>llama3.2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>contrary_v6</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>check-in</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Contrary(P)Body(N)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>252</v>
+      </c>
+      <c r="H4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I4" t="n">
+        <v>111</v>
+      </c>
+      <c r="J4" t="n">
+        <v>47</v>
+      </c>
+      <c r="K4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.419753</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.361702</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.388571</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.575397</v>
       </c>
     </row>
   </sheetData>
@@ -666,31 +784,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.4235294117647059</v>
+        <v>0.421053</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3829787234042553</v>
+        <v>0.368794</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4022346368715084</v>
+        <v>0.393195</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5753968253968254</v>
+        <v>0.575397</v>
       </c>
       <c r="J2" t="n">
-        <v>252</v>
+        <v>756</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="L2" t="n">
-        <v>109</v>
+        <v>331</v>
       </c>
       <c r="M2" t="n">
-        <v>49</v>
+        <v>143</v>
       </c>
       <c r="N2" t="n">
-        <v>58</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
